--- a/output/pdf_financials_xlsx/FSZ.xlsx
+++ b/output/pdf_financials_xlsx/FSZ.xlsx
@@ -37036,7 +37036,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
+          <t>CashEquivalents</t>
         </is>
       </c>
       <c r="E356" s="5" t="n">

--- a/output/pdf_financials_xlsx/FSZ.xlsx
+++ b/output/pdf_financials_xlsx/FSZ.xlsx
@@ -850,7 +850,7 @@
         <v>5835</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>103420</v>
+        <v>15984</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>125.72</v>
@@ -899,7 +899,7 @@
         <v>9042</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-79207</v>
+        <v>8229</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>28.007</v>
@@ -2043,16 +2043,16 @@
         <v>2118278</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1714569</v>
+        <v>1177</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>6016</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>21.774</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>16.88</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>25.725</v>
@@ -2141,16 +2141,16 @@
         <v>2118278</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1714569</v>
+        <v>1177</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>6016</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>21.774</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>16.88</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>25.725</v>
@@ -2738,7 +2738,7 @@
         <v>3771</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>30.099</v>
+        <v>13.219</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>20.963</v>
@@ -6551,16 +6551,16 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-17.53</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-17.962</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-16.345</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-14.271</v>
       </c>
     </row>
     <row r="125">
@@ -6602,16 +6602,16 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-17.53</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-17.962</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-16.345</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-14.271</v>
       </c>
     </row>
     <row r="126">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -37036,7 +37036,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E356" s="5" t="n">
@@ -39492,7 +39492,11 @@
           <t>Lease payments (Note 13)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -41358,7 +41362,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -64276,7 +64284,7 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -64295,10 +64303,10 @@
         </is>
       </c>
       <c r="H684" s="5" t="n">
-        <v>-15984</v>
+        <v>15984</v>
       </c>
       <c r="I684" s="5" t="n">
-        <v>-9875</v>
+        <v>9875</v>
       </c>
       <c r="J684" t="inlineStr">
         <is>
@@ -66572,7 +66580,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -66591,10 +66599,10 @@
         </is>
       </c>
       <c r="H711" s="5" t="n">
-        <v>-22213</v>
+        <v>22213</v>
       </c>
       <c r="I711" s="5" t="n">
-        <v>-36923</v>
+        <v>36923</v>
       </c>
       <c r="J711" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FSZ.xlsx
+++ b/output/pdf_financials_xlsx/FSZ.xlsx
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3186</v>
+        <v>1434269</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>5022.173</v>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-1431083</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>2.934</v>
@@ -1586,10 +1586,10 @@
         <v>0.23</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.03</v>
+        <v>0.22</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0.06</v>
@@ -1637,10 +1637,10 @@
         <v>0.23</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.03</v>
+        <v>0.22</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0.06</v>
@@ -1688,10 +1688,10 @@
         <v>13852.173913</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>182.166667</v>
+        <v>24.840909</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>10259.090909</v>
+        <v>9404.166667</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>88766.666667</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3186</v>
+        <v>1434269</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>5022.173</v>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>99.77786593728234</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>0.0584209265590811</v>
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>8297440</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>15896754</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>15942</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>29888</v>
@@ -2824,10 +2824,10 @@
         <v>88360</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>-1625027</v>
+        <v>4514231</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0</v>
+        <v>4514</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>6532</v>
@@ -3241,13 +3241,13 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>452037</v>
+        <v>2758694</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>229061</v>
+        <v>2706158</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
+        <v>2598</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>5200</v>
@@ -3290,13 +3290,13 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>249416</v>
+        <v>21876238</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>138700</v>
+        <v>48933744</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>141219</v>
+        <v>194627</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>360460</v>
@@ -3345,7 +3345,7 @@
         <v>89904685</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>90470456</v>
+        <v>89905</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>278750</v>
@@ -4713,16 +4713,16 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>30724786</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>10069079</v>
+        <v>134495560</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>134496</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>135587</v>
       </c>
       <c r="F88" s="3" t="n">
         <v>0</v>
@@ -24768,7 +24768,11 @@
           <t>Investments Note 7 6,532</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -24852,7 +24856,11 @@
           <t>Accounts receivable Note 8 29,888</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -25364,7 +25372,11 @@
           <t>Property and equipment Note 9 5,200</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -25448,7 +25460,11 @@
           <t>Intangible assets Note 10 180,230</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -25532,7 +25548,11 @@
           <t>Goodwill Note 10 278,750</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -26552,7 +26572,11 @@
           <t>Long term debt Note 14 107,521</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>LongTermDebt</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -26898,7 +26922,11 @@
           <t>Share capital Note 15 307,759</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -29094,7 +29122,11 @@
           <t>Restricted cash NOTE 5</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -29178,7 +29210,11 @@
           <t>Investments NOTE 6</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -29262,7 +29298,11 @@
           <t>Accounts receivable NOTE 7</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -29430,7 +29470,11 @@
           <t>Long-term investment NOTE 8</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -29514,7 +29558,11 @@
           <t>Property and equipment NOTE 9</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -29598,7 +29646,11 @@
           <t>Intangible assets NOTE 10</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -30608,7 +30660,11 @@
           <t>Share capital NOTE 15</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -33260,7 +33316,11 @@
           <t>Restricted cash NOTE 6</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E312" s="5" t="n">
         <v>1569632</v>
       </c>
@@ -33344,7 +33404,11 @@
           <t>Investments NOTE 7</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -33430,7 +33494,11 @@
           <t>Accounts receivable NOTE 8</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E314" s="5" t="n">
         <v>8297440</v>
       </c>
@@ -33774,7 +33842,11 @@
           <t>Capital assets NOTE 10</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E318" s="5" t="n">
         <v>2306657</v>
       </c>
@@ -33858,7 +33930,11 @@
           <t>Intangible assets NOTE 11</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E319" s="5" t="n">
         <v>21626822</v>
       </c>
@@ -34372,7 +34448,11 @@
           <t>Share capital NOTE 17</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E325" s="5" t="n">
         <v>30724786</v>
       </c>
@@ -73150,7 +73230,11 @@
           <t>Income taxes Note 13</t>
         </is>
       </c>
-      <c r="D788" t="inlineStr"/>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E788" t="inlineStr">
         <is>
           <t>-</t>
@@ -73234,7 +73318,11 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="D789" t="inlineStr"/>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E789" t="inlineStr">
         <is>
           <t>-</t>
@@ -73246,10 +73334,10 @@
         </is>
       </c>
       <c r="G789" s="5" t="n">
-        <v>0.24</v>
+        <v>2.4e-07</v>
       </c>
       <c r="H789" s="5" t="n">
-        <v>0.06</v>
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="I789" t="inlineStr">
         <is>
@@ -73318,7 +73406,11 @@
           <t>Diluted</t>
         </is>
       </c>
-      <c r="D790" t="inlineStr"/>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E790" t="inlineStr">
         <is>
           <t>-</t>
@@ -73330,10 +73422,10 @@
         </is>
       </c>
       <c r="G790" s="5" t="n">
-        <v>0.24</v>
+        <v>2.4e-07</v>
       </c>
       <c r="H790" s="5" t="n">
-        <v>0.06</v>
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="I790" t="inlineStr">
         <is>
@@ -76568,7 +76660,11 @@
           <t>Future income taxes NOTE 14</t>
         </is>
       </c>
-      <c r="D828" t="inlineStr"/>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E828" t="inlineStr">
         <is>
           <t>-</t>
@@ -76738,17 +76834,21 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="D830" t="inlineStr"/>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E830" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F830" s="5" t="n">
-        <v>0.00022</v>
+        <v>2.2e-07</v>
       </c>
       <c r="G830" s="5" t="n">
-        <v>0.00025</v>
+        <v>2.5e-07</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
@@ -76822,17 +76922,21 @@
           <t>Diluted</t>
         </is>
       </c>
-      <c r="D831" t="inlineStr"/>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E831" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F831" s="5" t="n">
-        <v>0.00022</v>
+        <v>2.2e-07</v>
       </c>
       <c r="G831" s="5" t="n">
-        <v>0.00024</v>
+        <v>2.4e-07</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
@@ -79048,7 +79152,11 @@
           <t>Future income taxes NOTE 16</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E857" s="5" t="n">
         <v>1431083</v>
       </c>

--- a/output/pdf_financials_xlsx/FSZ.xlsx
+++ b/output/pdf_financials_xlsx/FSZ.xlsx
@@ -1785,34 +1785,34 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>281209</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1372.552</v>
+        <v>1374.378</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.44</v>
+        <v>12595</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>12.609</v>
+        <v>23032</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>19.083</v>
+        <v>20.424</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>25.7</v>
+        <v>27.433</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>27.119</v>
+        <v>29.149</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>42.723</v>
+        <v>46.124</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>44.927</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>49.048</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>57.622</v>
@@ -1846,22 +1846,22 @@
         <v>3046</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>41.077</v>
+        <v>42.418</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>54.449</v>
+        <v>56.182</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>59.554</v>
+        <v>61.584</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>64.928</v>
+        <v>68.32899999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>14.868</v>
+        <v>59.795</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.184</v>
+        <v>43.864</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>99.267</v>
@@ -1895,22 +1895,22 @@
         <v>12.5800189980589</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>26.7207452171707</v>
+        <v>27.59307083336044</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>24.48708838899432</v>
+        <v>25.26646219160093</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>23.04569745798458</v>
+        <v>23.83124949209998</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>18.86652099121298</v>
+        <v>19.85477009623878</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>3.238538344921324</v>
+        <v>13.02450903514733</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-0.9594936005996835</v>
+        <v>8.118678105074174</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>14.56726133960633</v>
@@ -5288,31 +5288,31 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1372.552</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>4.252</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>13.745</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>20.424</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>27.433</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>29.149</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>46.124</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>44.927</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>49.048</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>57.622</v>
@@ -42118,7 +42118,11 @@
           <t>Amortization of intangible assets and depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -46694,7 +46698,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -46772,7 +46780,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -58470,7 +58478,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -58556,7 +58564,11 @@
           <t>Depreciation of property and equipment (Note 10)</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E615" t="inlineStr">
         <is>
           <t>-</t>
@@ -60134,7 +60146,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -60214,7 +60226,11 @@
           <t>Depreciation of property and equipment (Note 11)</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E635" t="inlineStr">
         <is>
           <t>-</t>
@@ -61406,7 +61422,7 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -62248,7 +62264,11 @@
           <t>Depreciation of property and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E659" t="inlineStr">
         <is>
           <t>-</t>
@@ -63686,7 +63706,11 @@
           <t>Depreciation of property &amp; equipment 367 326 259</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E676" t="inlineStr">
         <is>
           <t>-</t>
@@ -63703,10 +63727,10 @@
         </is>
       </c>
       <c r="H676" s="5" t="n">
-        <v>-108</v>
+        <v>108</v>
       </c>
       <c r="I676" s="5" t="n">
-        <v>-41</v>
+        <v>41</v>
       </c>
       <c r="J676" t="inlineStr">
         <is>
@@ -63772,7 +63796,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -63791,10 +63815,10 @@
         </is>
       </c>
       <c r="H677" s="5" t="n">
-        <v>-2500</v>
+        <v>2500</v>
       </c>
       <c r="I677" s="5" t="n">
-        <v>-1780</v>
+        <v>1780</v>
       </c>
       <c r="J677" t="inlineStr">
         <is>
@@ -65982,7 +66006,11 @@
           <t>Depreciation of property &amp; equipment 1,341 934 1,136</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E703" t="inlineStr">
         <is>
           <t>-</t>
@@ -65999,10 +66027,10 @@
         </is>
       </c>
       <c r="H703" s="5" t="n">
-        <v>-205</v>
+        <v>205</v>
       </c>
       <c r="I703" s="5" t="n">
-        <v>-407</v>
+        <v>407</v>
       </c>
       <c r="J703" t="inlineStr">
         <is>
@@ -66068,7 +66096,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -66087,10 +66115,10 @@
         </is>
       </c>
       <c r="H704" s="5" t="n">
-        <v>-6474</v>
+        <v>6474</v>
       </c>
       <c r="I704" s="5" t="n">
-        <v>-7358</v>
+        <v>7358</v>
       </c>
       <c r="J704" t="inlineStr">
         <is>
@@ -67854,7 +67882,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E725" t="inlineStr">
         <is>
           <t>-</t>
@@ -67938,7 +67970,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -69382,7 +69414,11 @@
           <t>Depreciation of property and equipment 259 228 202</t>
         </is>
       </c>
-      <c r="D743" t="inlineStr"/>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E743" t="inlineStr">
         <is>
           <t>-</t>
@@ -69394,10 +69430,10 @@
         </is>
       </c>
       <c r="G743" s="5" t="n">
-        <v>-57</v>
+        <v>57</v>
       </c>
       <c r="H743" s="5" t="n">
-        <v>-31</v>
+        <v>31</v>
       </c>
       <c r="I743" t="inlineStr">
         <is>
@@ -69468,7 +69504,7 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
@@ -69482,10 +69518,10 @@
         </is>
       </c>
       <c r="G744" s="5" t="n">
-        <v>-2780</v>
+        <v>2780</v>
       </c>
       <c r="H744" s="5" t="n">
-        <v>-64</v>
+        <v>64</v>
       </c>
       <c r="I744" t="inlineStr">
         <is>
@@ -71182,7 +71218,7 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -71196,10 +71232,10 @@
         </is>
       </c>
       <c r="G764" s="5" t="n">
-        <v>-5506</v>
+        <v>5506</v>
       </c>
       <c r="H764" s="5" t="n">
-        <v>-9170</v>
+        <v>9170</v>
       </c>
       <c r="I764" t="inlineStr">
         <is>
@@ -74096,7 +74132,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
@@ -74105,7 +74141,7 @@
         </is>
       </c>
       <c r="F798" s="5" t="n">
-        <v>-1.826</v>
+        <v>1.826</v>
       </c>
       <c r="G798" s="5" t="n">
         <v>1.373</v>
@@ -75810,7 +75846,7 @@
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E818" s="5" t="n">
@@ -77868,7 +77904,7 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E842" s="5" t="n">

--- a/output/pdf_financials_xlsx/FSZ.xlsx
+++ b/output/pdf_financials_xlsx/FSZ.xlsx
@@ -3158,31 +3158,31 @@
         <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>11.879</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>25.261</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>28.568</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>31.053</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>34.002</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>55.048</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>56.035</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>57.272</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>53.534</v>
       </c>
     </row>
     <row r="57">
@@ -3207,31 +3207,31 @@
         <v>0</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>6.848</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>10.372</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>13.769</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>17.804</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>31.673</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>36.255</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>40.419</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>37.638</v>
       </c>
     </row>
     <row r="58">
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.200815</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>6.670515</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -3550,31 +3550,31 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>11.989</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>12.947</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>22.302</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>29.555</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>36.298</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>65.604</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>70.518</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>56.301</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>50.775</v>
       </c>
     </row>
     <row r="65">
@@ -5663,13 +5663,13 @@
         <v>5.43</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>-5.813</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>-1.382</v>
+        <v>16.904</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>-1.333</v>
+        <v>23.635</v>
       </c>
       <c r="L107" s="3" t="n">
         <v>20.639</v>
@@ -6104,31 +6104,31 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-255.806</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.781</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-2.336</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-48.224</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-2.343</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-1.655</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-2.942</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-21.543</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-11.297</v>
       </c>
       <c r="L116" s="3" t="n">
         <v>0</v>
@@ -6261,10 +6261,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D119" s="3" t="n">
+        <v>10176.758</v>
       </c>
       <c r="E119" s="3" t="n">
         <v>-107.631</v>
@@ -6287,25 +6285,17 @@
       <c r="K119" s="3" t="n">
         <v>-110.745</v>
       </c>
-      <c r="L119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L119" s="3" t="n">
+        <v>-6.34</v>
+      </c>
+      <c r="M119" s="3" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="N119" s="3" t="n">
+        <v>9.388999999999999</v>
+      </c>
+      <c r="O119" s="3" t="n">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="120">
@@ -6810,10 +6800,8 @@
       <c r="D129" s="3" t="n">
         <v>-10186.411</v>
       </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" s="3" t="n">
+        <v>95.79300000000001</v>
       </c>
       <c r="F129" s="3" t="n">
         <v>181.918</v>
@@ -6824,20 +6812,14 @@
       <c r="H129" s="3" t="n">
         <v>-25.852</v>
       </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="3" t="n">
+        <v>101.494</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>-65.887</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>16.811</v>
       </c>
       <c r="L129" s="3" t="n">
         <v>-148.15</v>
@@ -7123,15 +7105,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>7.182</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>15.495</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>34.43</v>
@@ -7142,40 +7120,26 @@
       <c r="H135" s="3" t="n">
         <v>57.447</v>
       </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="3" t="n">
+        <v>53.521</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>89.286</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>103.782</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>113.31</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>137.967</v>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>134.004</v>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>133.587</v>
       </c>
     </row>
   </sheetData>
@@ -38502,7 +38466,11 @@
           <t>Net cash generated by operating activities</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -42516,7 +42484,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -42598,7 +42570,11 @@
           <t>Cash settled share-based compensation expense</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -43412,7 +43388,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -43642,7 +43622,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -46200,7 +46184,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -48350,7 +48338,11 @@
           <t>Net cash generated from (used in) ﬁnancing activities</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -50722,7 +50714,11 @@
           <t>Purchase of intangible assets (Note 10)</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -53806,7 +53802,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -54570,7 +54570,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E566" t="inlineStr">
         <is>
           <t>-</t>
@@ -59470,7 +59474,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E626" t="inlineStr">
         <is>
           <t>-</t>
